--- a/docs/downloads/05/tbl_latrine_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_latrine_alaotra_tous.xlsx
@@ -387,12 +387,6 @@
           <t>Dans la nature</t>
         </is>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>6.5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -495,12 +489,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -513,12 +501,6 @@
           <t>Fosse septique en individuel</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -531,12 +513,6 @@
           <t>Dans la nature</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -639,12 +615,6 @@
           <t>Fosse septique en individuel</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -747,12 +717,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -765,12 +729,6 @@
           <t>Fosse septique en individuel</t>
         </is>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -783,12 +741,6 @@
           <t>Dans la nature</t>
         </is>
       </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -837,12 +789,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -855,12 +801,6 @@
           <t>Dans la nature</t>
         </is>
       </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28">
-        <v>5.5</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -963,12 +903,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C34">
-        <v>3</v>
-      </c>
-      <c r="D34">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -980,12 +914,6 @@
         <is>
           <t>Fosse septique en individuel</t>
         </is>
-      </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
-      <c r="D35">
-        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/05/tbl_latrine_alaotra_tous.xlsx
+++ b/docs/downloads/05/tbl_latrine_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -427,7 +427,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,7 +445,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -907,7 +907,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
